--- a/data/distances.xlsx
+++ b/data/distances.xlsx
@@ -8,12 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/andrewhsu/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834A04AA-7A8E-A248-A098-9738A3FAA117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72CD5E7E-6EA4-7645-80FD-3B15E3A37154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38300" yWindow="700" windowWidth="38200" windowHeight="20800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38300" yWindow="700" windowWidth="38200" windowHeight="20800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Pearson distances" sheetId="1" r:id="rId1"/>
+    <sheet name="Euclidean distances" sheetId="3" r:id="rId2"/>
+    <sheet name="Euclidean distances (Euclidean)" sheetId="4" r:id="rId3"/>
+    <sheet name="Euclidean distances (log2)" sheetId="6" r:id="rId4"/>
+    <sheet name="TEC" sheetId="7" r:id="rId5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="22">
   <si>
     <t>Category</t>
   </si>
@@ -97,7 +101,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,6 +120,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFD8DEE9"/>
       <name val="Menlo"/>
       <family val="2"/>
     </font>
@@ -226,23 +236,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -530,365 +547,2011 @@
     <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="39.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="41.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="6">
         <v>15889</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="6">
         <v>0.48055300000000001</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="7">
         <v>0.52595700000000001</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="14">
+      <c r="I2" s="13">
         <v>5.9949080599999995E-14</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="9">
+      <c r="B3" s="6">
         <v>1605</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="6">
         <v>0.76955300000000004</v>
       </c>
-      <c r="D3" s="10">
+      <c r="D3" s="7">
         <v>0.75054699999999996</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <v>1.51648518E-102</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="6">
         <v>419</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="6">
         <v>0.69443699999999997</v>
       </c>
-      <c r="D4" s="10">
+      <c r="D4" s="7">
         <v>0.68591400000000002</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="18">
+        <v>2.1824226799999999E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="6">
+        <v>185</v>
+      </c>
+      <c r="C5" s="6">
+        <v>0.74724699999999999</v>
+      </c>
+      <c r="D5" s="7">
+        <v>0.77249699999999999</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="18">
+        <v>1.8444102699999998E-33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="6">
+        <v>36</v>
+      </c>
+      <c r="C6" s="6">
+        <v>0.74224500000000004</v>
+      </c>
+      <c r="D6" s="7">
+        <v>0.729549</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="18">
+        <v>9.7328198999999999E-57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="6">
+        <v>65</v>
+      </c>
+      <c r="C7" s="6">
+        <v>0.58773399999999998</v>
+      </c>
+      <c r="D7" s="7">
+        <v>0.61282700000000001</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="14">
+        <v>0.77682008000000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="6">
+        <v>25</v>
+      </c>
+      <c r="C8" s="6">
+        <v>0.54086599999999996</v>
+      </c>
+      <c r="D8" s="7">
+        <v>0.54513900000000004</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="14">
+        <v>0.22668350000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="6">
+        <v>108</v>
+      </c>
+      <c r="C9" s="6">
+        <v>0.65133099999999999</v>
+      </c>
+      <c r="D9" s="7">
+        <v>0.59962899999999997</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="14">
+        <v>0.36290735000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1185</v>
+      </c>
+      <c r="C10" s="6">
+        <v>0.82385699999999995</v>
+      </c>
+      <c r="D10" s="7">
+        <v>0.77395599999999998</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="14">
+        <v>0.72319911999999997</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="6">
+        <v>511</v>
+      </c>
+      <c r="C11" s="6">
+        <v>0.85584899999999997</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.837947</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="13">
+        <v>2.2606026899999999E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="6">
+        <v>92</v>
+      </c>
+      <c r="C12" s="6">
+        <v>0.93619300000000005</v>
+      </c>
+      <c r="D12" s="7">
+        <v>0.80343600000000004</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="14">
+        <v>0.74841756000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="6">
+        <v>145</v>
+      </c>
+      <c r="C13" s="6">
+        <v>0.90817099999999995</v>
+      </c>
+      <c r="D13" s="7">
+        <v>0.83357599999999998</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="14">
+        <v>0.47594455000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="6">
+        <v>86</v>
+      </c>
+      <c r="C14" s="6">
+        <v>0.63542100000000001</v>
+      </c>
+      <c r="D14" s="7">
+        <v>0.65379299999999996</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="14">
+        <v>8.6779000000000001E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="6">
+        <v>351</v>
+      </c>
+      <c r="C15" s="6">
+        <v>0.64666599999999996</v>
+      </c>
+      <c r="D15" s="7">
+        <v>0.67788000000000004</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="13">
+        <v>0.33759109300000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="8">
+        <v>3673</v>
+      </c>
+      <c r="C16" s="8">
+        <v>1.0778639999999999</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0.94331600000000004</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="17">
+        <v>3.8451523600000003E-12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08D215B-37AE-3F4C-BDEA-C33DA3AEB81B}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="20">
+        <v>15889</v>
+      </c>
+      <c r="C2" s="20">
+        <v>46.725707999999997</v>
+      </c>
+      <c r="D2" s="7">
+        <v>232.862199</v>
+      </c>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="18">
+        <v>5.8420235500000004E-3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="13" t="s">
+      <c r="B3" s="20">
+        <v>1605</v>
+      </c>
+      <c r="C3" s="20">
+        <v>20.301449999999999</v>
+      </c>
+      <c r="D3" s="7">
+        <v>541.21180600000002</v>
+      </c>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="18">
+        <v>7.1778768999999999E-60</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="14">
-        <v>4.9148700599999998E-3</v>
+      <c r="B4" s="20">
+        <v>419</v>
+      </c>
+      <c r="C4" s="20">
+        <v>35.920690999999998</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1159.3408509999999</v>
+      </c>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="18">
+        <v>1.3126132E-8</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="20">
         <v>185</v>
       </c>
-      <c r="C5" s="9">
-        <v>0.74724699999999999</v>
-      </c>
-      <c r="D5" s="10">
-        <v>0.77249699999999999</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="C5" s="20">
+        <v>39.870556000000001</v>
+      </c>
+      <c r="D5" s="7">
+        <v>470.50768399999998</v>
+      </c>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="18">
+        <v>2.6806511299999999E-98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="20">
+        <v>36</v>
+      </c>
+      <c r="C6" s="20">
+        <v>8.8263560000000005</v>
+      </c>
+      <c r="D6" s="7">
+        <v>105.400806</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="18">
+        <v>2.3795516300000001E-122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="20">
+        <v>65</v>
+      </c>
+      <c r="C7" s="20">
+        <v>20.188825000000001</v>
+      </c>
+      <c r="D7" s="7">
+        <v>76.522401000000002</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1.0912420000000001E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="20">
+        <v>25</v>
+      </c>
+      <c r="C8" s="20">
+        <v>33.498139999999999</v>
+      </c>
+      <c r="D8" s="7">
+        <v>191.63413499999999</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0.47171264000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="20">
+        <v>108</v>
+      </c>
+      <c r="C9" s="20">
+        <v>61.581017000000003</v>
+      </c>
+      <c r="D9" s="7">
+        <v>3566.3023760000001</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0.54613842999999995</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="20">
+        <v>1185</v>
+      </c>
+      <c r="C10" s="20">
+        <v>14.620564999999999</v>
+      </c>
+      <c r="D10" s="7">
+        <v>322.58144800000002</v>
+      </c>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0.49495062000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="20">
+        <v>511</v>
+      </c>
+      <c r="C11" s="20">
+        <v>7.4901309999999999</v>
+      </c>
+      <c r="D11" s="7">
+        <v>131.482271</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="18">
+        <v>0.80083313</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="20">
+        <v>92</v>
+      </c>
+      <c r="C12" s="20">
+        <v>7.9342949999999997</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1080.7193609999999</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="7">
+        <v>7.9170050000000006E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="20">
+        <v>145</v>
+      </c>
+      <c r="C13" s="20">
+        <v>9.4524589999999993</v>
+      </c>
+      <c r="D13" s="7">
+        <v>104.142422</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="7">
+        <v>0.36628722000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="20">
+        <v>86</v>
+      </c>
+      <c r="C14" s="20">
+        <v>2.5755880000000002</v>
+      </c>
+      <c r="D14" s="7">
+        <v>226.47798399999999</v>
+      </c>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="7">
+        <v>0.1011861</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="20">
+        <v>351</v>
+      </c>
+      <c r="C15" s="20">
+        <v>62.827210000000001</v>
+      </c>
+      <c r="D15" s="7">
+        <v>515.862212</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="18">
+        <v>2.9261920299999999E-12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="8">
+        <v>3673</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.40112799999999998</v>
+      </c>
+      <c r="D16" s="9">
+        <v>475.99135699999999</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="22">
+        <v>5.6234199999999997E-22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A7C34D6-7F09-1A4B-97A7-EECC09096DCC}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="20">
+        <v>15889</v>
+      </c>
+      <c r="C2" s="20">
+        <v>1.1349999999999999E-3</v>
+      </c>
+      <c r="D2" s="7">
+        <v>3.4910000000000002E-3</v>
+      </c>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="18">
+        <v>5.3673374299999997E-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="B3" s="20">
+        <v>1605</v>
+      </c>
+      <c r="C3" s="20">
+        <v>2.5700000000000001E-4</v>
+      </c>
+      <c r="D3" s="7">
+        <v>4.1720000000000004E-3</v>
+      </c>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="21" t="s">
         <v>13</v>
       </c>
+      <c r="I3" s="18">
+        <v>3.5480877000000003E-111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="20">
+        <v>419</v>
+      </c>
+      <c r="C4" s="20">
+        <v>7.8700000000000005E-4</v>
+      </c>
+      <c r="D4" s="7">
+        <v>7.4130000000000003E-3</v>
+      </c>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="18">
+        <v>3.60926165E-14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="20">
+        <v>185</v>
+      </c>
+      <c r="C5" s="20">
+        <v>8.5700000000000001E-4</v>
+      </c>
+      <c r="D5" s="7">
+        <v>4.385E-3</v>
+      </c>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="18">
+        <v>1.5506107599999999E-100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="20">
+        <v>36</v>
+      </c>
+      <c r="C6" s="20">
+        <v>1.9900000000000001E-4</v>
+      </c>
+      <c r="D6" s="7">
+        <v>1.5989999999999999E-3</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="18">
+        <v>7.1283859200000002E-66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="20">
+        <v>65</v>
+      </c>
+      <c r="C7" s="20">
+        <v>4.9899999999999999E-4</v>
+      </c>
+      <c r="D7" s="7">
+        <v>1.341E-3</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="7">
+        <v>1.073561E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="20">
+        <v>25</v>
+      </c>
+      <c r="C8" s="20">
+        <v>3.7800000000000003E-4</v>
+      </c>
+      <c r="D8" s="7">
+        <v>4.8399999999999997E-3</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0.58264793999999998</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="20">
+        <v>108</v>
+      </c>
+      <c r="C9" s="20">
+        <v>1.088E-3</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1.8787000000000002E-2</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0.33510158000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="20">
+        <v>1185</v>
+      </c>
+      <c r="C10" s="20">
+        <v>2.13E-4</v>
+      </c>
+      <c r="D10" s="7">
+        <v>3.0249999999999999E-3</v>
+      </c>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0.74924782999999995</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="20">
+        <v>511</v>
+      </c>
+      <c r="C11" s="20">
+        <v>1.21E-4</v>
+      </c>
+      <c r="D11" s="7">
+        <v>1.4580000000000001E-3</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="18">
+        <v>0.91066564500000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="20">
+        <v>92</v>
+      </c>
+      <c r="C12" s="20">
+        <v>1.1400000000000001E-4</v>
+      </c>
+      <c r="D12" s="7">
+        <v>7.1630000000000001E-3</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="7">
+        <v>0.1204742</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="20">
+        <v>145</v>
+      </c>
+      <c r="C13" s="20">
+        <v>1.54E-4</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1.3760000000000001E-3</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="7">
+        <v>0.20579294000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="20">
+        <v>86</v>
+      </c>
+      <c r="C14" s="20">
+        <v>6.7000000000000002E-5</v>
+      </c>
+      <c r="D14" s="7">
+        <v>2.5720000000000001E-3</v>
+      </c>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="7">
+        <v>3.7224340000000002E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="20">
+        <v>351</v>
+      </c>
+      <c r="C15" s="20">
+        <v>9.4700000000000003E-4</v>
+      </c>
+      <c r="D15" s="7">
+        <v>5.0130000000000001E-3</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="18">
+        <v>1.4273205699999999E-13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="8">
+        <v>3673</v>
+      </c>
+      <c r="C16" s="8">
+        <v>7.9999999999999996E-6</v>
+      </c>
+      <c r="D16" s="9">
+        <v>2.879E-3</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="22">
+        <v>1.0734589799999999E-22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8357939E-0B7C-BD4F-9FD1-B5D09BA096A4}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="20">
+        <v>15889</v>
+      </c>
+      <c r="C2" s="20">
+        <v>3.0373570000000001</v>
+      </c>
+      <c r="D2" s="7">
+        <v>3.4323510000000002</v>
+      </c>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="18">
+        <v>5.9949080599999995E-14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="20">
+        <v>1605</v>
+      </c>
+      <c r="C3" s="20">
+        <v>3.4408660000000002</v>
+      </c>
+      <c r="D3" s="7">
+        <v>4.3626740000000002</v>
+      </c>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="18">
+        <v>0.21522838699999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="20">
+        <v>419</v>
+      </c>
+      <c r="C4" s="20">
+        <v>3.3650479999999998</v>
+      </c>
+      <c r="D4" s="7">
+        <v>4.2688969999999999</v>
+      </c>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="18">
+        <v>0.18391069500000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="20">
+        <v>185</v>
+      </c>
+      <c r="C5" s="20">
+        <v>4.4988010000000003</v>
+      </c>
+      <c r="D5" s="7">
+        <v>5.2426469999999998</v>
+      </c>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I5" s="18">
+        <v>4.7691036600000002E-108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="20">
+        <v>36</v>
+      </c>
+      <c r="C6" s="20">
+        <v>3.0020910000000001</v>
+      </c>
+      <c r="D6" s="7">
+        <v>3.2698140000000002</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="12"/>
+      <c r="G6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="18">
+        <v>5.2057320799999997E-170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="20">
+        <v>65</v>
+      </c>
+      <c r="C7" s="20">
+        <v>3.289412</v>
+      </c>
+      <c r="D7" s="7">
+        <v>3.6939649999999999</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="7">
+        <v>8.4433500000000005E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="20">
+        <v>25</v>
+      </c>
+      <c r="C8" s="20">
+        <v>2.4665840000000001</v>
+      </c>
+      <c r="D8" s="7">
+        <v>3.1811820000000002</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+      <c r="G8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0.48049037</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="20">
+        <v>108</v>
+      </c>
+      <c r="C9" s="20">
+        <v>2.699014</v>
+      </c>
+      <c r="D9" s="7">
+        <v>3.5317379999999998</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0.40215838999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="20">
+        <v>1185</v>
+      </c>
+      <c r="C10" s="20">
+        <v>3.536511</v>
+      </c>
+      <c r="D10" s="7">
+        <v>4.391775</v>
+      </c>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0.88779211999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="20">
+        <v>511</v>
+      </c>
+      <c r="C11" s="20">
+        <v>1.945789</v>
+      </c>
+      <c r="D11" s="7">
+        <v>4.0641949999999998</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="18">
+        <v>2.2578118E-4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="20">
+        <v>92</v>
+      </c>
+      <c r="C12" s="20">
+        <v>2.5165060000000001</v>
+      </c>
+      <c r="D12" s="7">
+        <v>3.0535299999999999</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="7">
+        <v>0.74841756000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="20">
+        <v>145</v>
+      </c>
+      <c r="C13" s="20">
+        <v>3.1165419999999999</v>
+      </c>
+      <c r="D13" s="7">
+        <v>3.8425220000000002</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="7">
+        <v>0.47594455000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="20">
+        <v>86</v>
+      </c>
+      <c r="C14" s="20">
+        <v>1.313078</v>
+      </c>
+      <c r="D14" s="7">
+        <v>3.2274630000000002</v>
+      </c>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="7">
+        <v>8.6779000000000001E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="20">
+        <v>351</v>
+      </c>
+      <c r="C15" s="20">
+        <v>5.2948909999999998</v>
+      </c>
+      <c r="D15" s="7">
+        <v>5.731617</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="18">
+        <v>1.6165027799999999E-9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="8">
+        <v>3673</v>
+      </c>
+      <c r="C16" s="8">
+        <v>0.107907</v>
+      </c>
+      <c r="D16" s="9">
+        <v>1.1827859999999999</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="I16" s="22">
+        <v>9.1144273100000001E-10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB7C4B2B-6B00-0243-BAC6-F1DEE91BA3B3}">
+  <dimension ref="A1:I16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="39.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="41.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="6">
+        <v>15889</v>
+      </c>
+      <c r="C2" s="19">
+        <v>6.25E-2</v>
+      </c>
+      <c r="D2" s="19">
+        <v>7.2523000000000004E-2</v>
+      </c>
+      <c r="G2" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="10">
+        <v>4.1804599299999997E-25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6">
+        <v>1605</v>
+      </c>
+      <c r="C3" s="19">
+        <v>0.125</v>
+      </c>
+      <c r="D3" s="19">
+        <v>0.16456399999999999</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="10">
+        <v>1.0248387E-99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="6">
+        <v>419</v>
+      </c>
+      <c r="C4" s="19">
+        <v>6.25E-2</v>
+      </c>
+      <c r="D4" s="19">
+        <v>0.18019099999999999</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4" s="10">
+        <v>0.99826916600000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="6">
+        <v>185</v>
+      </c>
+      <c r="C5" s="19">
+        <v>0.25</v>
+      </c>
+      <c r="D5" s="19">
+        <v>0.250338</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>7</v>
+      </c>
       <c r="I5" s="10">
-        <v>0.14466047000000001</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="7" t="s">
+        <v>8.7572520099999991E-19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="6">
         <v>36</v>
       </c>
-      <c r="C6" s="9">
-        <v>0.74224500000000004</v>
-      </c>
-      <c r="D6" s="10">
-        <v>0.729549</v>
-      </c>
-      <c r="G6" s="1" t="s">
+      <c r="C6" s="19">
+        <v>0.125</v>
+      </c>
+      <c r="D6" s="19">
+        <v>0.159722</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="10">
+        <v>5.3960879299999997E-59</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="6">
+        <v>65</v>
+      </c>
+      <c r="C7" s="19">
+        <v>6.25E-2</v>
+      </c>
+      <c r="D7" s="19">
+        <v>0.165385</v>
+      </c>
+      <c r="G7" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="10">
-        <v>0.77682008000000002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="7" t="s">
+      <c r="I7" s="19">
+        <v>3.029248E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="6">
+        <v>25</v>
+      </c>
+      <c r="C8" s="19">
+        <v>6.25E-2</v>
+      </c>
+      <c r="D8" s="19">
+        <v>8.5000000000000006E-2</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="H8" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="9">
-        <v>65</v>
-      </c>
-      <c r="C7" s="9">
-        <v>0.58773399999999998</v>
-      </c>
-      <c r="D7" s="10">
-        <v>0.61282700000000001</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="13" t="s">
+      <c r="I8" s="19">
+        <v>0.95970078999999997</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="6">
+        <v>108</v>
+      </c>
+      <c r="C9" s="19">
+        <v>3.125E-2</v>
+      </c>
+      <c r="D9" s="19">
+        <v>9.7800999999999999E-2</v>
+      </c>
+      <c r="G9" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="10">
-        <v>0.22668350000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="7" t="s">
+      <c r="H9" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="9">
-        <v>25</v>
-      </c>
-      <c r="C8" s="9">
-        <v>0.54086599999999996</v>
-      </c>
-      <c r="D8" s="10">
-        <v>0.54513900000000004</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="13" t="s">
+      <c r="I9" s="19">
+        <v>4.9296180000000002E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1185</v>
+      </c>
+      <c r="C10" s="19">
+        <v>0.125</v>
+      </c>
+      <c r="D10" s="19">
+        <v>0.15912399999999999</v>
+      </c>
+      <c r="G10" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="10">
-        <v>0.36290735000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="7" t="s">
+      <c r="H10" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="9">
-        <v>108</v>
-      </c>
-      <c r="C9" s="9">
-        <v>0.65133099999999999</v>
-      </c>
-      <c r="D9" s="10">
-        <v>0.59962899999999997</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="13" t="s">
+      <c r="I10" s="19">
+        <v>0.93862383000000005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="6">
+        <v>511</v>
+      </c>
+      <c r="C11" s="19">
+        <v>9.375E-2</v>
+      </c>
+      <c r="D11" s="19">
+        <v>0.157444</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="H11" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="10">
-        <v>0.72319911999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="9">
-        <v>1185</v>
-      </c>
-      <c r="C10" s="9">
-        <v>0.82385699999999995</v>
-      </c>
-      <c r="D10" s="10">
-        <v>0.77395599999999998</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H10" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="I10" s="14">
-        <v>2.2606026899999999E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="7" t="s">
+      <c r="I11" s="10">
+        <v>8.2667740300000008E-9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="6">
+        <v>92</v>
+      </c>
+      <c r="C12" s="19">
+        <v>0.11057699999999999</v>
+      </c>
+      <c r="D12" s="19">
+        <v>0.182589</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="9">
-        <v>511</v>
-      </c>
-      <c r="C11" s="9">
-        <v>0.85584899999999997</v>
-      </c>
-      <c r="D11" s="10">
-        <v>0.837947</v>
-      </c>
-      <c r="G11" s="1" t="s">
+      <c r="H12" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="19">
+        <v>0.71734699000000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="6">
+        <v>145</v>
+      </c>
+      <c r="C13" s="19">
+        <v>0.14583299999999999</v>
+      </c>
+      <c r="D13" s="19">
+        <v>0.162914</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="19">
+        <v>0.83327693999999997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="6">
+        <v>86</v>
+      </c>
+      <c r="C14" s="19">
+        <v>2.0833000000000001E-2</v>
+      </c>
+      <c r="D14" s="19">
+        <v>0.104869</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="19">
+        <v>2.6407499999999999E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="6">
+        <v>351</v>
+      </c>
+      <c r="C15" s="19">
+        <v>0.15625</v>
+      </c>
+      <c r="D15" s="19">
+        <v>0.16714799999999999</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="10">
+        <v>5.2313319699999999E-5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="8">
+        <v>3673</v>
+      </c>
+      <c r="C16" s="19">
+        <v>5.7470000000000004E-3</v>
+      </c>
+      <c r="D16" s="19">
+        <v>4.8835999999999997E-2</v>
+      </c>
+      <c r="G16" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="10">
-        <v>0.74841756000000004</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="9">
-        <v>92</v>
-      </c>
-      <c r="C12" s="9">
-        <v>0.93619300000000005</v>
-      </c>
-      <c r="D12" s="10">
-        <v>0.80343600000000004</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="10">
-        <v>0.47594455000000002</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A13" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="9">
-        <v>145</v>
-      </c>
-      <c r="C13" s="9">
-        <v>0.90817099999999995</v>
-      </c>
-      <c r="D13" s="10">
-        <v>0.83357599999999998</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="10">
-        <v>8.6779000000000001E-4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="9">
-        <v>86</v>
-      </c>
-      <c r="C14" s="9">
-        <v>0.63542100000000001</v>
-      </c>
-      <c r="D14" s="10">
-        <v>0.65379299999999996</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="H14" s="13" t="s">
+      <c r="H16" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="I14" s="14">
-        <v>0.33759109300000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="9">
-        <v>351</v>
-      </c>
-      <c r="C15" s="9">
-        <v>0.64666599999999996</v>
-      </c>
-      <c r="D15" s="10">
-        <v>0.67788000000000004</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I15" s="15">
-        <v>3.8451523600000003E-12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="11">
-        <v>3673</v>
-      </c>
-      <c r="C16" s="11">
-        <v>1.0778639999999999</v>
-      </c>
-      <c r="D16" s="12">
-        <v>0.94331600000000004</v>
+      <c r="I16" s="10">
+        <v>0.14265496899999999</v>
       </c>
     </row>
   </sheetData>
